--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17530,6 +17530,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B747" t="n">
+        <v>0</v>
+      </c>
+      <c r="C747" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="D747" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="E747" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="F747" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="G747" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17553,6 +17553,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B748" t="n">
+        <v>0</v>
+      </c>
+      <c r="C748" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="D748" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="E748" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="F748" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="G748" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17576,6 +17576,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B749" t="n">
+        <v>0</v>
+      </c>
+      <c r="C749" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="D749" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="E749" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="F749" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="G749" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17599,6 +17599,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B750" t="n">
+        <v>0</v>
+      </c>
+      <c r="C750" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="D750" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="E750" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="F750" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="G750" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B751" t="n">
+        <v>34290</v>
+      </c>
+      <c r="C751" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D751" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E751" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F751" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G751" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17463,7 +17463,7 @@
     </row>
     <row r="744">
       <c r="A744" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B744" t="n">
         <v>0</v>
@@ -17486,22 +17486,22 @@
     </row>
     <row r="745">
       <c r="A745" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B745" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="C745" t="n">
-        <v>1.99000000953674</v>
+        <v>2</v>
       </c>
       <c r="D745" t="n">
-        <v>1.94000005722046</v>
+        <v>2</v>
       </c>
       <c r="E745" t="n">
-        <v>1.94000005722046</v>
+        <v>2</v>
       </c>
       <c r="F745" t="n">
-        <v>1.99000000953674</v>
+        <v>2</v>
       </c>
       <c r="G745" t="s">
         <v>7</v>
@@ -17509,19 +17509,19 @@
     </row>
     <row r="746">
       <c r="A746" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B746" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="C746" t="n">
         <v>1.99000000953674</v>
       </c>
       <c r="D746" t="n">
-        <v>1.99000000953674</v>
+        <v>1.94000005722046</v>
       </c>
       <c r="E746" t="n">
-        <v>1.99000000953674</v>
+        <v>1.94000005722046</v>
       </c>
       <c r="F746" t="n">
         <v>1.99000000953674</v>
@@ -17532,7 +17532,7 @@
     </row>
     <row r="747">
       <c r="A747" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B747" t="n">
         <v>0</v>
@@ -17555,7 +17555,7 @@
     </row>
     <row r="748">
       <c r="A748" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B748" t="n">
         <v>0</v>
@@ -17578,7 +17578,7 @@
     </row>
     <row r="749">
       <c r="A749" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B749" t="n">
         <v>0</v>
@@ -17601,7 +17601,7 @@
     </row>
     <row r="750">
       <c r="A750" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B750" t="n">
         <v>0</v>
@@ -17624,22 +17624,22 @@
     </row>
     <row r="751">
       <c r="A751" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B751" t="n">
-        <v>34290</v>
+        <v>0</v>
       </c>
       <c r="C751" t="n">
-        <v>1.97000002861023</v>
+        <v>1.99000000953674</v>
       </c>
       <c r="D751" t="n">
-        <v>1.97000002861023</v>
+        <v>1.99000000953674</v>
       </c>
       <c r="E751" t="n">
-        <v>1.97000002861023</v>
+        <v>1.99000000953674</v>
       </c>
       <c r="F751" t="n">
-        <v>1.97000002861023</v>
+        <v>1.99000000953674</v>
       </c>
       <c r="G751" t="s">
         <v>7</v>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17645,6 +17645,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B752" t="n">
+        <v>34290</v>
+      </c>
+      <c r="C752" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D752" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E752" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F752" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G752" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B753" t="n">
+        <v>0</v>
+      </c>
+      <c r="C753" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D753" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E753" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F753" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G753" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -20005,6 +20005,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B756" t="n">
+        <v>540</v>
+      </c>
+      <c r="C756" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D756" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E756" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F756" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G756" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="H756" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17760,6 +17760,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B757" t="n">
+        <v>0</v>
+      </c>
+      <c r="C757" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D757" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E757" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F757" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G757" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17783,6 +17783,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B758" t="n">
+        <v>0</v>
+      </c>
+      <c r="C758" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D758" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E758" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F758" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G758" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17806,6 +17806,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B759" t="n">
+        <v>0</v>
+      </c>
+      <c r="C759" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D759" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E759" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F759" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G759" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17829,6 +17829,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B760" t="n">
+        <v>0</v>
+      </c>
+      <c r="C760" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D760" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E760" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F760" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G760" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17852,6 +17852,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="761">
+      <c r="A761" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B761" t="n">
+        <v>0</v>
+      </c>
+      <c r="C761" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D761" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E761" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F761" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G761" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17875,6 +17875,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B762" t="n">
+        <v>0</v>
+      </c>
+      <c r="C762" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D762" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E762" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F762" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G762" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17898,6 +17898,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B763" t="n">
+        <v>0</v>
+      </c>
+      <c r="C763" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D763" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E763" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F763" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G763" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17921,6 +17921,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="764">
+      <c r="A764" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B764" t="n">
+        <v>0</v>
+      </c>
+      <c r="C764" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="D764" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="E764" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F764" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G764" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B765" t="n">
+        <v>270</v>
+      </c>
+      <c r="C765" t="n">
+        <v>2</v>
+      </c>
+      <c r="D765" t="n">
+        <v>2</v>
+      </c>
+      <c r="E765" t="n">
+        <v>2</v>
+      </c>
+      <c r="F765"/>
+      <c r="G765" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17960,7 +17960,9 @@
       <c r="E765" t="n">
         <v>2</v>
       </c>
-      <c r="F765"/>
+      <c r="F765" t="n">
+        <v>2</v>
+      </c>
       <c r="G765" t="s">
         <v>7</v>
       </c>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -17967,6 +17967,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B766" t="n">
+        <v>0</v>
+      </c>
+      <c r="C766" t="n">
+        <v>2</v>
+      </c>
+      <c r="D766" t="n">
+        <v>2</v>
+      </c>
+      <c r="E766" t="n">
+        <v>2</v>
+      </c>
+      <c r="F766" t="n">
+        <v>2</v>
+      </c>
+      <c r="G766" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B767" t="n">
+        <v>64260</v>
+      </c>
+      <c r="C767" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D767" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E767" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F767"/>
+      <c r="G767" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -18006,8 +18006,31 @@
       <c r="E767" t="n">
         <v>1.97000002861023</v>
       </c>
-      <c r="F767"/>
+      <c r="F767" t="n">
+        <v>1.97000002861023</v>
+      </c>
       <c r="G767" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B768" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C768" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D768" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E768" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F768"/>
+      <c r="G768" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -18036,6 +18036,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B769" t="n">
+        <v>0</v>
+      </c>
+      <c r="C769" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D769" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E769" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F769" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G769" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -18059,6 +18059,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B770" t="n">
+        <v>0</v>
+      </c>
+      <c r="C770" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D770" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E770" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F770" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G770" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -18082,6 +18082,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B771" t="n">
+        <v>0</v>
+      </c>
+      <c r="C771" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D771" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E771" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F771" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G771" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -18105,6 +18105,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B772" t="n">
+        <v>0</v>
+      </c>
+      <c r="C772" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D772" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E772" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F772" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G772" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22795,6 +22795,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="s">
+        <v>9</v>
+      </c>
+      <c r="B774" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C774" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D774" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E774" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F774" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G774" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H774" t="n">
+        <v>0</v>
+      </c>
+      <c r="I774" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22824,6 +22824,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="775">
+      <c r="A775" t="s">
+        <v>9</v>
+      </c>
+      <c r="B775" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C775" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D775" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E775" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F775" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G775" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H775" t="n">
+        <v>0</v>
+      </c>
+      <c r="I775" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22853,6 +22853,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="776">
+      <c r="A776" t="s">
+        <v>9</v>
+      </c>
+      <c r="B776" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C776" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D776" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E776" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F776" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G776" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H776" t="n">
+        <v>0</v>
+      </c>
+      <c r="I776" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22882,6 +22882,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="777">
+      <c r="A777" t="s">
+        <v>9</v>
+      </c>
+      <c r="B777" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C777" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D777" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E777" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F777" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G777" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H777" t="n">
+        <v>0</v>
+      </c>
+      <c r="I777" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22911,6 +22911,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="778">
+      <c r="A778" t="s">
+        <v>9</v>
+      </c>
+      <c r="B778" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C778" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D778" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E778" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F778" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G778" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H778" t="n">
+        <v>0</v>
+      </c>
+      <c r="I778" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22940,6 +22940,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="779">
+      <c r="A779" t="s">
+        <v>9</v>
+      </c>
+      <c r="B779" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C779" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D779" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E779" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F779" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="G779" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="H779" t="n">
+        <v>0</v>
+      </c>
+      <c r="I779" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="s">
+        <v>9</v>
+      </c>
+      <c r="B780" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C780" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="D780" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E780" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="F780" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G780" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="H780" t="n">
+        <v>1890</v>
+      </c>
+      <c r="I780" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -22998,6 +22998,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="s">
+        <v>9</v>
+      </c>
+      <c r="B781" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C781" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D781" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E781" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F781" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G781" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="H781" t="n">
+        <v>0</v>
+      </c>
+      <c r="I781" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="s">
+        <v>9</v>
+      </c>
+      <c r="B782" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C782" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D782" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E782" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F782" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G782" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="H782" t="n">
+        <v>21330</v>
+      </c>
+      <c r="I782" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLC.MI.xlsx
+++ b/data/VLC.MI.xlsx
@@ -23056,6 +23056,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="783">
+      <c r="A783" t="s">
+        <v>9</v>
+      </c>
+      <c r="B783" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C783" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D783" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E783" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F783" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="G783" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="H783" t="n">
+        <v>7290</v>
+      </c>
+      <c r="I783" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
